--- a/IWA SM Analytics.xlsx
+++ b/IWA SM Analytics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe298b740ac8d92e/Escritorio/IWA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="486" documentId="11_F25DC773A252ABDACC1048A411DB46485BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CB1815-27E0-45CD-8E98-4C7764C35B22}"/>
+  <xr:revisionPtr revIDLastSave="508" documentId="11_F25DC773A252ABDACC1048A411DB46485BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B38B1BB-AA6A-49E5-85AE-B929E1072DD5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="21">
   <si>
     <t>Posts</t>
   </si>
@@ -99,13 +99,16 @@
   </si>
   <si>
     <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +119,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -443,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
@@ -704,14 +713,38 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2">
+        <v>288</v>
+      </c>
+      <c r="D12" s="2">
+        <v>385</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE65EA43-C5B5-461B-97F3-AA52C64BF321}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
@@ -972,14 +1005,38 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2">
+        <v>460</v>
+      </c>
+      <c r="D12" s="2">
+        <v>186</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F899F49E-9B34-4877-B9A8-1F5FE7EFF951}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
@@ -1240,7 +1297,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2">
+        <v>582</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
